--- a/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición</t>
+          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>122,52; 131,82</t>
+          <t>122,55; 131,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121,45; 131,9</t>
+          <t>121,65; 131,84</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134,15; 145,23</t>
+          <t>134,16; 145,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,04; 137,26</t>
+          <t>126,76; 137,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>122,32; 131,45</t>
+          <t>122,67; 132,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>138,64; 149,39</t>
+          <t>138,44; 149,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>126,03; 133,02</t>
+          <t>126,18; 133,16</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>123,44; 130,36</t>
+          <t>123,39; 130,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138,29; 146,46</t>
+          <t>138,56; 146,2</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>120,4; 129,68</t>
+          <t>120,59; 129,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127,49; 136,17</t>
+          <t>127,68; 136,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,94; 144,35</t>
+          <t>132,95; 144,43</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123,62; 132,19</t>
+          <t>123,59; 131,9</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,89; 134,38</t>
+          <t>126,57; 134,48</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>133,83; 145,26</t>
+          <t>133,37; 145,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,37; 129,76</t>
+          <t>123,28; 129,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>128,18; 134,07</t>
+          <t>128,27; 134,0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135,55; 143,57</t>
+          <t>135,02; 143,64</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126,05; 134,88</t>
+          <t>125,39; 134,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125,65; 136,74</t>
+          <t>126,14; 137,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118,76; 137,67</t>
+          <t>118,66; 137,58</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121,28; 131,75</t>
+          <t>120,83; 132,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,87; 138,69</t>
+          <t>127,01; 138,06</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132,72; 147,46</t>
+          <t>132,02; 147,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,98; 132,2</t>
+          <t>124,93; 132,46</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,17; 136,19</t>
+          <t>128,59; 136,21</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129,6; 141,3</t>
+          <t>129,37; 141,34</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125,89; 132,06</t>
+          <t>125,77; 132,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129,66; 135,17</t>
+          <t>129,98; 135,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130,1; 151,32</t>
+          <t>130,14; 152,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125,74; 131,96</t>
+          <t>125,26; 131,46</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>129,45; 135,96</t>
+          <t>129,43; 135,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>131,47; 144,03</t>
+          <t>131,77; 143,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,29; 130,74</t>
+          <t>126,44; 130,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,37; 134,62</t>
+          <t>130,34; 134,77</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,15; 147,17</t>
+          <t>133,34; 147,52</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,25; 133,77</t>
+          <t>127,5; 134,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129,3; 136,21</t>
+          <t>129,4; 135,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132,45; 147,71</t>
+          <t>132,5; 146,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,72; 136,75</t>
+          <t>129,05; 137,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,55; 137,66</t>
+          <t>129,96; 137,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133,59; 143,57</t>
+          <t>133,76; 143,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>129,16; 134,53</t>
+          <t>129,39; 134,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,69; 135,8</t>
+          <t>130,97; 135,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134,87; 143,46</t>
+          <t>134,42; 143,24</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123,56; 139,6</t>
+          <t>123,2; 139,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129,01; 141,4</t>
+          <t>128,59; 141,1</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130,2; 144,44</t>
+          <t>130,26; 144,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>130,37; 140,99</t>
+          <t>129,62; 140,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129,82; 141,01</t>
+          <t>129,3; 140,98</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,16; 152,52</t>
+          <t>137,19; 152,95</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>129,17; 138,76</t>
+          <t>129,31; 138,72</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,81; 139,35</t>
+          <t>130,83; 139,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136,53; 147,47</t>
+          <t>136,67; 146,84</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,24; 130,69</t>
+          <t>127,12; 130,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>130,26; 133,74</t>
+          <t>130,41; 133,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135,13; 145,5</t>
+          <t>134,95; 145,99</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128,43; 132,12</t>
+          <t>128,43; 132,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>130,32; 133,73</t>
+          <t>130,32; 133,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>137,47; 142,76</t>
+          <t>137,48; 142,66</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>128,45; 131,05</t>
+          <t>128,43; 130,84</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130,97; 133,28</t>
+          <t>130,79; 133,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>137,2; 142,74</t>
+          <t>137,38; 142,58</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Talla media, en centímetros, recogida tras medición (tasa de respuesta: 93,78%)</t>
+          <t>Talla media, en centímetros, recogida por medición (tasa de respuesta: 93,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>122,55; 131,7</t>
+          <t>122,82; 132,47</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>121,65; 131,84</t>
+          <t>122,08; 132,27</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134,16; 145,26</t>
+          <t>133,4; 144,94</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,76; 137,67</t>
+          <t>126,68; 137,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>122,67; 132,02</t>
+          <t>122,38; 131,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>138,44; 149,48</t>
+          <t>138,7; 149,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>126,18; 133,16</t>
+          <t>126,01; 132,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>123,39; 130,02</t>
+          <t>123,24; 130,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>138,56; 146,2</t>
+          <t>137,94; 146,17</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>120,59; 129,81</t>
+          <t>120,48; 129,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>127,68; 136,14</t>
+          <t>128,29; 136,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>132,95; 144,43</t>
+          <t>133,28; 144,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123,59; 131,9</t>
+          <t>123,53; 132,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,57; 134,48</t>
+          <t>126,57; 134,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>133,37; 145,5</t>
+          <t>133,85; 145,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,28; 129,55</t>
+          <t>123,39; 129,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>128,27; 134,0</t>
+          <t>128,26; 134,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135,02; 143,64</t>
+          <t>135,26; 143,47</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>125,39; 134,69</t>
+          <t>126,02; 134,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126,14; 137,25</t>
+          <t>125,48; 136,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>118,66; 137,58</t>
+          <t>119,29; 138,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>120,83; 132,04</t>
+          <t>121,05; 132,2</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,01; 138,06</t>
+          <t>127,98; 139,01</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132,02; 147,42</t>
+          <t>132,03; 147,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,93; 132,46</t>
+          <t>124,96; 131,97</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,59; 136,21</t>
+          <t>128,59; 136,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129,37; 141,34</t>
+          <t>129,35; 141,99</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125,77; 132,21</t>
+          <t>125,88; 131,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129,98; 135,38</t>
+          <t>129,84; 135,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130,14; 152,05</t>
+          <t>130,75; 152,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125,26; 131,46</t>
+          <t>125,43; 131,62</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>129,43; 135,61</t>
+          <t>129,22; 135,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>131,77; 143,87</t>
+          <t>131,21; 143,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,44; 130,88</t>
+          <t>126,41; 131,06</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,34; 134,77</t>
+          <t>130,52; 134,73</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,34; 147,52</t>
+          <t>133,42; 147,38</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,5; 134,29</t>
+          <t>127,13; 133,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129,4; 135,99</t>
+          <t>129,32; 136,02</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132,5; 146,89</t>
+          <t>132,54; 147,56</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>129,05; 137,14</t>
+          <t>128,68; 137,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>129,96; 137,4</t>
+          <t>130,4; 137,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133,76; 143,17</t>
+          <t>133,56; 143,33</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>129,39; 134,58</t>
+          <t>129,12; 134,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,97; 135,96</t>
+          <t>130,77; 135,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134,42; 143,24</t>
+          <t>134,77; 143,24</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123,2; 139,84</t>
+          <t>123,61; 139,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>128,59; 141,1</t>
+          <t>129,25; 141,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>130,26; 144,6</t>
+          <t>131,08; 144,07</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129,62; 140,62</t>
+          <t>129,97; 141,01</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129,3; 140,98</t>
+          <t>129,46; 140,78</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,19; 152,95</t>
+          <t>137,68; 152,52</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>129,31; 138,72</t>
+          <t>128,52; 138,28</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,83; 139,24</t>
+          <t>130,87; 139,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136,67; 146,84</t>
+          <t>136,22; 146,92</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,12; 130,69</t>
+          <t>127,25; 130,64</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>130,41; 133,68</t>
+          <t>130,4; 133,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134,95; 145,99</t>
+          <t>135,12; 144,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128,43; 132,17</t>
+          <t>128,31; 131,92</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>130,32; 133,75</t>
+          <t>130,33; 133,8</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>137,48; 142,66</t>
+          <t>137,62; 142,76</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>128,43; 130,84</t>
+          <t>128,41; 130,89</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130,79; 133,18</t>
+          <t>130,78; 133,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>137,38; 142,58</t>
+          <t>137,17; 142,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ28_T-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>131,93</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>126,77</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>145,09</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>127,45</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>126,64</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>139,83</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>131,93</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>126,77</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>144,48</t>
+          <t>140,8</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>142,58</t>
+          <t>143,28</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>122,82; 132,47</t>
+          <t>126,04; 137,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>122,08; 132,27</t>
+          <t>122,32; 131,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>133,4; 144,94</t>
+          <t>139,32; 149,93</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>126,68; 137,02</t>
+          <t>122,52; 131,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>122,38; 131,74</t>
+          <t>121,45; 131,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>138,7; 149,37</t>
+          <t>135,24; 146,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>126,01; 132,84</t>
+          <t>126,03; 133,02</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>123,24; 130,4</t>
+          <t>123,44; 130,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137,94; 146,17</t>
+          <t>139,09; 147,01</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>127,71</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>130,33</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>140,45</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>125,1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>132,08</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>139,11</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>127,71</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>130,33</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>139,49</t>
+          <t>139,94</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139,3</t>
+          <t>140,19</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>120,48; 129,44</t>
+          <t>123,62; 132,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>128,29; 136,47</t>
+          <t>126,89; 134,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>133,28; 144,86</t>
+          <t>134,83; 146,32</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123,53; 132,53</t>
+          <t>120,4; 129,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>126,57; 134,39</t>
+          <t>127,49; 136,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>133,85; 145,23</t>
+          <t>134,0; 145,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>123,39; 129,49</t>
+          <t>123,37; 129,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>128,26; 134,03</t>
+          <t>128,18; 134,07</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135,26; 143,47</t>
+          <t>136,43; 144,43</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>126,6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>133,19</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>141,27</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>130,51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>131,32</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>129,33</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>126,6</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>133,19</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>139,18</t>
+          <t>130,33</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>135,51</t>
+          <t>136,8</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>126,02; 134,83</t>
+          <t>121,28; 131,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125,48; 136,57</t>
+          <t>127,87; 138,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>119,29; 138,16</t>
+          <t>135,2; 149,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121,05; 132,2</t>
+          <t>126,05; 134,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>127,98; 139,01</t>
+          <t>125,65; 136,74</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>132,03; 147,38</t>
+          <t>120,73; 138,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>124,96; 131,97</t>
+          <t>124,98; 132,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>128,59; 136,4</t>
+          <t>128,17; 136,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>129,35; 141,99</t>
+          <t>130,94; 142,38</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>128,48</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>132,51</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>137,76</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>128,96</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>132,49</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>140,03</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>128,48</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>132,51</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>137,02</t>
+          <t>136,0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>138,63</t>
+          <t>136,92</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>125,88; 131,95</t>
+          <t>125,74; 131,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>129,84; 135,16</t>
+          <t>129,45; 135,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130,75; 152,61</t>
+          <t>132,44; 144,41</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>125,43; 131,62</t>
+          <t>125,89; 132,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>129,22; 135,57</t>
+          <t>129,66; 135,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>131,21; 143,55</t>
+          <t>130,4; 140,87</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>126,41; 131,06</t>
+          <t>126,29; 130,74</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>130,52; 134,73</t>
+          <t>130,37; 134,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>133,42; 147,38</t>
+          <t>133,48; 140,88</t>
         </is>
       </c>
     </row>
@@ -1064,47 +1064,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>132,91</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>134,1</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>139,88</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>130,66</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>132,75</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>137,59</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>131,75</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>133,43</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>138,97</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>132,91</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>134,1</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>138,64</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>131,75</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>133,43</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>138,77</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>127,13; 133,76</t>
+          <t>128,72; 136,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>129,32; 136,02</t>
+          <t>130,55; 137,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132,54; 147,56</t>
+          <t>134,89; 144,79</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>128,68; 137,16</t>
+          <t>127,25; 133,77</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>130,4; 137,83</t>
+          <t>129,3; 136,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>133,56; 143,33</t>
+          <t>130,46; 143,06</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>129,12; 134,03</t>
+          <t>129,16; 134,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>130,77; 135,68</t>
+          <t>130,69; 135,8</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>134,77; 143,24</t>
+          <t>135,28; 142,97</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>135,34</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>135,21</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>148,87</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>131,73</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>135,46</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>137,81</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>135,34</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>135,21</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>145,34</t>
+          <t>139,67</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>142,2</t>
+          <t>144,79</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>123,61; 139,58</t>
+          <t>130,37; 140,99</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>129,25; 141,03</t>
+          <t>129,82; 141,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>131,08; 144,07</t>
+          <t>142,15; 155,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>129,97; 141,01</t>
+          <t>123,56; 139,6</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>129,46; 140,78</t>
+          <t>129,01; 141,4</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>137,68; 152,52</t>
+          <t>132,78; 146,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>128,52; 138,28</t>
+          <t>129,17; 138,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>130,87; 139,26</t>
+          <t>130,81; 139,35</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>136,22; 146,92</t>
+          <t>139,76; 149,81</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>130,21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>132,07</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>141,47</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>129,03</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>131,97</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>138,71</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>130,21</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>132,07</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>140,15</t>
+          <t>137,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>139,49</t>
+          <t>139,77</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>127,25; 130,64</t>
+          <t>128,43; 132,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>130,4; 133,68</t>
+          <t>130,32; 133,73</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135,12; 144,6</t>
+          <t>138,86; 143,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>128,31; 131,92</t>
+          <t>127,24; 130,69</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>130,33; 133,8</t>
+          <t>130,26; 133,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>137,62; 142,76</t>
+          <t>135,24; 140,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>128,41; 130,89</t>
+          <t>128,45; 131,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>130,78; 133,14</t>
+          <t>130,97; 133,28</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>137,17; 142,87</t>
+          <t>138,0; 141,6</t>
         </is>
       </c>
     </row>
